--- a/rawData/TableForestCCycleSynthesis.3.xlsx
+++ b/rawData/TableForestCCycleSynthesis.3.xlsx
@@ -8,19 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valade/Documents/GitHub/Wood-Carbon/rawData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41A42FC-749E-6946-BBFB-9B8C6FE64614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149FF870-AE41-CF4F-873E-38BBC9E31B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38260" yWindow="-1900" windowWidth="30620" windowHeight="21000" xr2:uid="{D7314C47-DCFB-1A45-BB4B-0ADDE6497F76}"/>
+    <workbookView xWindow="-38260" yWindow="-3000" windowWidth="30620" windowHeight="21000" activeTab="2" xr2:uid="{D7314C47-DCFB-1A45-BB4B-0ADDE6497F76}"/>
   </bookViews>
   <sheets>
     <sheet name="processes" sheetId="1" r:id="rId1"/>
-    <sheet name="woodtype" sheetId="3" r:id="rId2"/>
-    <sheet name="Conversions" sheetId="2" r:id="rId3"/>
-    <sheet name="references" sheetId="4" r:id="rId4"/>
+    <sheet name="processes_for_ms" sheetId="6" r:id="rId2"/>
+    <sheet name="woodtype" sheetId="3" r:id="rId3"/>
+    <sheet name="woodtype_for_ms" sheetId="5" r:id="rId4"/>
+    <sheet name="Conversions" sheetId="2" r:id="rId5"/>
+    <sheet name="references" sheetId="4" r:id="rId6"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId7"/>
+  </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">processes!$A$1:$R$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">woodtype!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">processes!$A$1:$R$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">woodtype!$A$1:$N$1</definedName>
     <definedName name="C_to_CO2">Conversions!$B$4</definedName>
     <definedName name="kg_to_m3">Conversions!$B$2</definedName>
     <definedName name="t_to_m3">Conversions!$B$1</definedName>
@@ -120,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="168">
   <si>
     <t>Ex-situ</t>
   </si>
@@ -597,6 +602,33 @@
   </si>
   <si>
     <t>harvest</t>
+  </si>
+  <si>
+    <t>roundwood removals</t>
+  </si>
+  <si>
+    <t>FAO_2022</t>
+  </si>
+  <si>
+    <t>Flux type</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>Roundwood removals</t>
+  </si>
+  <si>
+    <t>FAO, 2022</t>
   </si>
 </sst>
 </file>
@@ -646,7 +678,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -654,15 +686,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -679,6 +724,28 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="processes"/>
+      <sheetName val="for_MS"/>
+      <sheetName val="Conversions"/>
+      <sheetName val="references"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -978,7 +1045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03E6F148-1FFC-7242-B550-BD89945A0684}">
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.6640625" customWidth="1"/>
@@ -1342,30 +1409,30 @@
         <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="H8" t="s">
-        <v>92</v>
-      </c>
-      <c r="K8">
-        <v>189</v>
+        <v>159</v>
+      </c>
+      <c r="K8" s="3">
+        <v>3911952000</v>
       </c>
       <c r="L8" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="M8" t="s">
-        <v>93</v>
-      </c>
-      <c r="N8" t="s">
-        <v>91</v>
+        <v>160</v>
+      </c>
+      <c r="N8">
+        <v>2020</v>
       </c>
       <c r="O8">
-        <f>K8*C_to_CO2</f>
-        <v>693.63</v>
+        <f>K8/tC_to_m3*C_to_CO2/10^6</f>
+        <v>3306.3857423519999</v>
       </c>
       <c r="P8">
-        <f t="shared" ref="P8:P13" si="0">O8/1000</f>
-        <v>0.69362999999999997</v>
+        <f>O8/1000</f>
+        <v>3.306385742352</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
@@ -1373,7 +1440,7 @@
         <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" t="s">
         <v>153</v>
@@ -1385,33 +1452,33 @@
         <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
         <v>141</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="K9">
-        <v>335</v>
+        <v>189</v>
       </c>
       <c r="L9" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="M9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9">
-        <v>2015</v>
+        <v>93</v>
+      </c>
+      <c r="N9" t="s">
+        <v>91</v>
       </c>
       <c r="O9">
-        <f>K9</f>
-        <v>335</v>
+        <f>K9*C_to_CO2</f>
+        <v>693.63</v>
       </c>
       <c r="P9">
-        <f t="shared" si="0"/>
-        <v>0.33500000000000002</v>
+        <f t="shared" ref="P9:P14" si="0">O9/1000</f>
+        <v>0.69362999999999997</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
@@ -1437,30 +1504,27 @@
         <v>141</v>
       </c>
       <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="K10">
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="L10" t="s">
         <v>22</v>
       </c>
       <c r="M10" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="N10">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="O10">
         <f>K10</f>
-        <v>200</v>
+        <v>335</v>
       </c>
       <c r="P10">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.33500000000000002</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
@@ -1485,29 +1549,31 @@
       <c r="G11" t="s">
         <v>141</v>
       </c>
-      <c r="J11" t="s">
-        <v>124</v>
+      <c r="H11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" t="s">
+        <v>50</v>
       </c>
       <c r="K11">
-        <f>0.47*10^9</f>
-        <v>470000000</v>
+        <v>200</v>
       </c>
       <c r="L11" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="M11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N11">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="O11">
-        <f>K11/10^6</f>
-        <v>470</v>
+        <f>K11</f>
+        <v>200</v>
       </c>
       <c r="P11">
         <f t="shared" si="0"/>
-        <v>0.47</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
@@ -1518,43 +1584,43 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>142</v>
-      </c>
-      <c r="H12" t="s">
-        <v>71</v>
+        <v>141</v>
+      </c>
+      <c r="J12" t="s">
+        <v>124</v>
       </c>
       <c r="K12">
-        <f>40+30</f>
-        <v>70</v>
+        <f>0.47*10^9</f>
+        <v>470000000</v>
       </c>
       <c r="L12" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="M12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N12">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="O12">
-        <f>K12</f>
-        <v>70</v>
+        <f>K12/10^6</f>
+        <v>470</v>
       </c>
       <c r="P12">
         <f t="shared" si="0"/>
-        <v>7.0000000000000007E-2</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.2">
@@ -1562,7 +1628,7 @@
         <v>157</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
         <v>152</v>
@@ -1571,42 +1637,37 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="H13" t="s">
-        <v>116</v>
-      </c>
-      <c r="I13" t="s">
-        <v>119</v>
-      </c>
-      <c r="J13" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="K13">
-        <v>2.4</v>
+        <f>40+30</f>
+        <v>70</v>
       </c>
       <c r="L13" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13" t="s">
-        <v>64</v>
+        <v>49</v>
+      </c>
+      <c r="N13">
+        <v>2007</v>
       </c>
       <c r="O13">
-        <f>K13*10^3</f>
-        <v>2400</v>
+        <f>K13</f>
+        <v>70</v>
       </c>
       <c r="P13">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>7.0000000000000007E-2</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
@@ -1623,34 +1684,42 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
         <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>143</v>
+        <v>140</v>
+      </c>
+      <c r="H14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" t="s">
+        <v>114</v>
       </c>
       <c r="K14">
-        <f>205+25+12+140+40+13</f>
-        <v>435</v>
+        <v>2.4</v>
       </c>
       <c r="L14" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="M14" t="s">
-        <v>49</v>
-      </c>
-      <c r="N14">
-        <v>2007</v>
+        <v>62</v>
+      </c>
+      <c r="N14" t="s">
+        <v>64</v>
       </c>
       <c r="O14">
-        <f>K14</f>
-        <v>435</v>
+        <f>K14*10^3</f>
+        <v>2400</v>
       </c>
       <c r="P14">
-        <f>O14/1000</f>
-        <v>0.435</v>
+        <f t="shared" si="0"/>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
@@ -1667,39 +1736,34 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15" t="s">
-        <v>139</v>
-      </c>
-      <c r="H15" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="K15">
-        <v>0.112</v>
+        <f>205+25+12+140+40+13</f>
+        <v>435</v>
       </c>
       <c r="L15" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="M15" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="N15">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="O15">
-        <f>K15*(references!D11)*C_to_CO2</f>
-        <v>821.24823595080909</v>
+        <f>K15</f>
+        <v>435</v>
       </c>
       <c r="P15">
-        <f>O15/10^3</f>
-        <v>0.82124823595080909</v>
+        <f>O15/1000</f>
+        <v>0.435</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.2">
@@ -1727,25 +1791,28 @@
       <c r="H16" t="s">
         <v>88</v>
       </c>
+      <c r="I16" t="s">
+        <v>89</v>
+      </c>
       <c r="K16">
-        <v>0.08</v>
+        <v>0.112</v>
       </c>
       <c r="L16" t="s">
         <v>84</v>
       </c>
       <c r="M16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="N16">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="O16">
         <f>K16*(references!D11)*C_to_CO2</f>
-        <v>586.60588282200649</v>
+        <v>821.24823595080909</v>
       </c>
       <c r="P16">
         <f>O16/10^3</f>
-        <v>0.58660588282200654</v>
+        <v>0.82124823595080909</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.2">
@@ -1773,31 +1840,25 @@
       <c r="H17" t="s">
         <v>88</v>
       </c>
-      <c r="I17" t="s">
-        <v>111</v>
-      </c>
-      <c r="J17" t="s">
-        <v>113</v>
-      </c>
       <c r="K17">
-        <v>142</v>
+        <v>0.08</v>
       </c>
       <c r="L17" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="M17" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="N17">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="O17">
-        <f>K17*C_to_CO2</f>
-        <v>521.14</v>
+        <f>K17*(references!D11)*C_to_CO2</f>
+        <v>586.60588282200649</v>
       </c>
       <c r="P17">
         <f>O17/10^3</f>
-        <v>0.52113999999999994</v>
+        <v>0.58660588282200654</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.2">
@@ -1826,13 +1887,13 @@
         <v>88</v>
       </c>
       <c r="I18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
         <v>113</v>
       </c>
       <c r="K18">
-        <v>497</v>
+        <v>142</v>
       </c>
       <c r="L18" t="s">
         <v>108</v>
@@ -1845,11 +1906,11 @@
       </c>
       <c r="O18">
         <f>K18*C_to_CO2</f>
-        <v>1823.99</v>
+        <v>521.14</v>
       </c>
       <c r="P18">
         <f>O18/10^3</f>
-        <v>1.82399</v>
+        <v>0.52113999999999994</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.2">
@@ -1857,7 +1918,7 @@
         <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" t="s">
         <v>152</v>
@@ -1869,33 +1930,39 @@
         <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>88</v>
+      </c>
+      <c r="I19" t="s">
+        <v>112</v>
+      </c>
+      <c r="J19" t="s">
+        <v>113</v>
       </c>
       <c r="K19">
-        <v>629</v>
+        <v>497</v>
       </c>
       <c r="L19" t="s">
-        <v>28</v>
+        <v>108</v>
       </c>
       <c r="M19" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
       <c r="N19">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="O19">
-        <f>K19/tC_to_m3*C_to_CO2</f>
-        <v>531.63142900000003</v>
+        <f>K19*C_to_CO2</f>
+        <v>1823.99</v>
       </c>
       <c r="P19">
-        <f t="shared" ref="P19:P25" si="1">O19/1000</f>
-        <v>0.53163142900000004</v>
+        <f>O19/10^3</f>
+        <v>1.82399</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.2">
@@ -1921,30 +1988,27 @@
         <v>148</v>
       </c>
       <c r="H20" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" t="s">
-        <v>118</v>
+        <v>34</v>
       </c>
       <c r="K20">
-        <v>162</v>
+        <v>629</v>
       </c>
       <c r="L20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N20">
         <v>2010</v>
       </c>
       <c r="O20">
-        <f>K20*C_to_CO2</f>
-        <v>594.54</v>
+        <f>K20/tC_to_m3*C_to_CO2</f>
+        <v>531.63142900000003</v>
       </c>
       <c r="P20">
-        <f t="shared" si="1"/>
-        <v>0.59453999999999996</v>
+        <f t="shared" ref="P20:P26" si="1">O20/1000</f>
+        <v>0.53163142900000004</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.2">
@@ -1970,28 +2034,30 @@
         <v>148</v>
       </c>
       <c r="H21" t="s">
-        <v>53</v>
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>118</v>
       </c>
       <c r="K21">
-        <f>20+250</f>
-        <v>270</v>
+        <v>162</v>
       </c>
       <c r="L21" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="M21" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="N21">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="O21">
-        <f>K21</f>
-        <v>270</v>
+        <f>K21*C_to_CO2</f>
+        <v>594.54</v>
       </c>
       <c r="P21">
         <f t="shared" si="1"/>
-        <v>0.27</v>
+        <v>0.59453999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.2">
@@ -2017,10 +2083,11 @@
         <v>148</v>
       </c>
       <c r="H22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K22">
-        <v>340</v>
+        <f>20+250</f>
+        <v>270</v>
       </c>
       <c r="L22" t="s">
         <v>22</v>
@@ -2033,11 +2100,11 @@
       </c>
       <c r="O22">
         <f>K22</f>
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="P22">
         <f t="shared" si="1"/>
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.2">
@@ -2060,33 +2127,30 @@
         <v>69</v>
       </c>
       <c r="G23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H23" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="K23">
-        <v>1863</v>
+        <v>340</v>
       </c>
       <c r="L23" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="N23">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="O23">
-        <f>K23/tC_to_m3*C_to_CO2</f>
-        <v>1574.6094629999998</v>
+        <f>K23</f>
+        <v>340</v>
       </c>
       <c r="P23">
         <f t="shared" si="1"/>
-        <v>1.5746094629999998</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.2">
@@ -2112,33 +2176,30 @@
         <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="I24" t="s">
         <v>16</v>
       </c>
-      <c r="J24" t="s">
-        <v>118</v>
-      </c>
       <c r="K24">
-        <v>591</v>
+        <v>1863</v>
       </c>
       <c r="L24" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="M24" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="N24">
         <v>2010</v>
       </c>
       <c r="O24">
-        <f>K24*C_to_CO2</f>
-        <v>2168.9699999999998</v>
+        <f>K24/tC_to_m3*C_to_CO2</f>
+        <v>1574.6094629999998</v>
       </c>
       <c r="P24">
         <f t="shared" si="1"/>
-        <v>2.1689699999999998</v>
+        <v>1.5746094629999998</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
@@ -2146,7 +2207,7 @@
         <v>157</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
         <v>152</v>
@@ -2158,19 +2219,22 @@
         <v>56</v>
       </c>
       <c r="F25" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G25" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="I25" t="s">
+        <v>16</v>
       </c>
       <c r="J25" t="s">
         <v>118</v>
       </c>
       <c r="K25">
-        <v>886</v>
+        <v>591</v>
       </c>
       <c r="L25" t="s">
         <v>13</v>
@@ -2183,11 +2247,11 @@
       </c>
       <c r="O25">
         <f>K25*C_to_CO2</f>
-        <v>3251.62</v>
+        <v>2168.9699999999998</v>
       </c>
       <c r="P25">
         <f t="shared" si="1"/>
-        <v>3.25162</v>
+        <v>2.1689699999999998</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
@@ -2213,27 +2277,30 @@
         <v>140</v>
       </c>
       <c r="H26" t="s">
-        <v>82</v>
+        <v>12</v>
+      </c>
+      <c r="J26" t="s">
+        <v>118</v>
       </c>
       <c r="K26">
-        <v>0.33</v>
+        <v>886</v>
       </c>
       <c r="L26" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="M26" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="N26">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="O26">
-        <f>K26*10^3*C_to_CO2</f>
-        <v>1211.0999999999999</v>
+        <f>K26*C_to_CO2</f>
+        <v>3251.62</v>
       </c>
       <c r="P26">
-        <f>K26*C_to_CO2</f>
-        <v>1.2111000000000001</v>
+        <f t="shared" si="1"/>
+        <v>3.25162</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
@@ -2262,21 +2329,24 @@
         <v>82</v>
       </c>
       <c r="K27">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="L27" t="s">
         <v>58</v>
       </c>
       <c r="M27" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="N27">
+        <v>2007</v>
       </c>
       <c r="O27">
         <f>K27*10^3*C_to_CO2</f>
-        <v>2385.5</v>
+        <v>1211.0999999999999</v>
       </c>
       <c r="P27">
         <f>K27*C_to_CO2</f>
-        <v>2.3855</v>
+        <v>1.2111000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
@@ -2287,7 +2357,7 @@
         <v>6</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2296,33 +2366,30 @@
         <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H28" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="K28">
-        <v>1.4</v>
+        <v>0.65</v>
       </c>
       <c r="L28" t="s">
         <v>58</v>
       </c>
       <c r="M28" t="s">
-        <v>149</v>
-      </c>
-      <c r="N28">
-        <v>2010</v>
+        <v>83</v>
       </c>
       <c r="O28">
         <f>K28*10^3*C_to_CO2</f>
-        <v>5138</v>
+        <v>2385.5</v>
       </c>
       <c r="P28">
         <f>K28*C_to_CO2</f>
-        <v>5.1379999999999999</v>
+        <v>2.3855</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
@@ -2348,27 +2415,27 @@
         <v>154</v>
       </c>
       <c r="H29" t="s">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="K29">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="L29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="M29" t="s">
-        <v>63</v>
-      </c>
-      <c r="N29" t="s">
-        <v>65</v>
+        <v>149</v>
+      </c>
+      <c r="N29">
+        <v>2010</v>
       </c>
       <c r="O29">
-        <f>K29*10^3</f>
-        <v>1600</v>
+        <f>K29*10^3*C_to_CO2</f>
+        <v>5138</v>
       </c>
       <c r="P29">
-        <f>O29/1000</f>
-        <v>1.6</v>
+        <f>K29*C_to_CO2</f>
+        <v>5.1379999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
@@ -2396,31 +2463,25 @@
       <c r="H30" t="s">
         <v>60</v>
       </c>
-      <c r="I30" t="s">
-        <v>119</v>
-      </c>
-      <c r="J30" t="s">
-        <v>118</v>
-      </c>
       <c r="K30">
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
       <c r="L30" t="s">
         <v>61</v>
       </c>
       <c r="M30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O30">
         <f>K30*10^3</f>
-        <v>7600</v>
+        <v>1600</v>
       </c>
       <c r="P30">
         <f>O30/1000</f>
-        <v>7.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
@@ -2446,19 +2507,19 @@
         <v>154</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>60</v>
       </c>
       <c r="I31" t="s">
         <v>119</v>
       </c>
       <c r="J31" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="K31">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>61</v>
       </c>
       <c r="M31" t="s">
         <v>62</v>
@@ -2468,11 +2529,11 @@
       </c>
       <c r="O31">
         <f>K31*10^3</f>
-        <v>3300</v>
+        <v>7600</v>
       </c>
       <c r="P31">
         <f>O31/1000</f>
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
@@ -2498,33 +2559,85 @@
         <v>154</v>
       </c>
       <c r="H32" t="s">
-        <v>60</v>
+        <v>117</v>
+      </c>
+      <c r="I32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J32" t="s">
+        <v>114</v>
       </c>
       <c r="K32">
-        <v>2.2000000000000002</v>
+        <v>3.3</v>
       </c>
       <c r="L32" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s">
-        <v>59</v>
-      </c>
-      <c r="N32">
-        <v>2017</v>
+        <v>62</v>
+      </c>
+      <c r="N32" t="s">
+        <v>64</v>
       </c>
       <c r="O32">
-        <f>K32*10^3*C_to_CO2</f>
-        <v>8074</v>
+        <f>K32*10^3</f>
+        <v>3300</v>
       </c>
       <c r="P32">
         <f>O32/1000</f>
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" t="s">
+        <v>68</v>
+      </c>
+      <c r="G33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H33" t="s">
+        <v>60</v>
+      </c>
+      <c r="K33">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="L33" t="s">
+        <v>58</v>
+      </c>
+      <c r="M33" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33">
+        <v>2017</v>
+      </c>
+      <c r="O33">
+        <f>K33*10^3*C_to_CO2</f>
+        <v>8074</v>
+      </c>
+      <c r="P33">
+        <f>O33/1000</f>
         <v>8.0739999999999998</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R32" xr:uid="{03E6F148-1FFC-7242-B550-BD89945A0684}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R32">
-      <sortCondition ref="D1:D32"/>
+  <autoFilter ref="A1:R33" xr:uid="{03E6F148-1FFC-7242-B550-BD89945A0684}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R33">
+      <sortCondition ref="D1:D33"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2533,6 +2646,741 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA902462-7601-0E4E-8714-74FBC3576D2B}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>2015</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4">
+        <v>2017</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C5" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>2010</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C6" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>2010</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C7" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7">
+        <v>2007</v>
+      </c>
+      <c r="G7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C8" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3911952000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>2020</v>
+      </c>
+      <c r="G9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C11" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C12" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>2015</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C13" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>2007</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C14" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>2015</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C16" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <v>2007</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C18" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18">
+        <v>2007</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C20" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20">
+        <v>2016</v>
+      </c>
+      <c r="G20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C21" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21">
+        <v>2009</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C22" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22">
+        <v>2015</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C23" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23">
+        <v>2015</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C25" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25">
+        <v>2010</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C26" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26">
+        <v>2010</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C27" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27">
+        <v>2007</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C28" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>2007</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C29" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>2010</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C30" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>2010</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C32" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>2010</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B33" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C33" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33">
+        <v>2007</v>
+      </c>
+      <c r="G33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B34" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C34" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B35" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C35" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B37" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C37" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37">
+        <v>2010</v>
+      </c>
+      <c r="G37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B38" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C38" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B39" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C39" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B40" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C40" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B41" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C41" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41">
+        <v>2017</v>
+      </c>
+      <c r="G41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E16AFC-4FAB-A542-91DA-733B44992E2F}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3040,7 +3888,742 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79CF63C-2DC4-0543-BD95-578BCB493AC5}">
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="27.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C3" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3">
+        <v>2015</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C4" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4">
+        <v>2017</v>
+      </c>
+      <c r="G4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B5" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C5" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5">
+        <v>2010</v>
+      </c>
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B6" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C6" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6">
+        <v>2010</v>
+      </c>
+      <c r="G6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B7" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C7" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7">
+        <v>2007</v>
+      </c>
+      <c r="G7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C8" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3911952000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>2020</v>
+      </c>
+      <c r="G9" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B11" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C11" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C12" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12">
+        <v>2015</v>
+      </c>
+      <c r="G12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C13" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13">
+        <v>2007</v>
+      </c>
+      <c r="G13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C14" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D14" t="s">
+        <v>54</v>
+      </c>
+      <c r="E14">
+        <v>2015</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B16" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C16" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16">
+        <v>2007</v>
+      </c>
+      <c r="G16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B18" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C18" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18">
+        <v>2007</v>
+      </c>
+      <c r="G18" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C20" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20">
+        <v>2016</v>
+      </c>
+      <c r="G20" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B21" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C21" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21">
+        <v>2009</v>
+      </c>
+      <c r="G21" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B22" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C22" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D22" t="s">
+        <v>108</v>
+      </c>
+      <c r="E22">
+        <v>2015</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C23" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D23" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23">
+        <v>2015</v>
+      </c>
+      <c r="G23" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B25" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C25" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25">
+        <v>2010</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B26" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C26" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26">
+        <v>2010</v>
+      </c>
+      <c r="G26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B27" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C27" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27">
+        <v>2007</v>
+      </c>
+      <c r="G27" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B28" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C28" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28">
+        <v>2007</v>
+      </c>
+      <c r="G28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B29" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C29" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29">
+        <v>2010</v>
+      </c>
+      <c r="G29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B30" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C30" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D30" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30">
+        <v>2010</v>
+      </c>
+      <c r="G30" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="5"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B32" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C32" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E32">
+        <v>2010</v>
+      </c>
+      <c r="G32" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B33" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C33" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D33" t="s">
+        <v>58</v>
+      </c>
+      <c r="E33">
+        <v>2007</v>
+      </c>
+      <c r="G33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B34" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C34" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D34" t="s">
+        <v>58</v>
+      </c>
+      <c r="G34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B35" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C35" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+      <c r="G35" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B37" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C37" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E37">
+        <v>2010</v>
+      </c>
+      <c r="G37" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B38" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C38" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D38" t="s">
+        <v>61</v>
+      </c>
+      <c r="E38" t="s">
+        <v>65</v>
+      </c>
+      <c r="G38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B39" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C39" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D39" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G39" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B40" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C40" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+      <c r="G40" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B41" t="e">
+        <f>PROPER(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C41" s="3" t="e">
+        <f>#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D41" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41">
+        <v>2017</v>
+      </c>
+      <c r="G41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5274EFC-FB99-DA43-B1E5-30C308D7C00A}">
   <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3118,7 +4701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AEC68F43-BBEE-E94A-AA3D-FDEC59433A9C}">
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
